--- a/PROJECT_OHRM/test_data/add_employee_data.xlsx
+++ b/PROJECT_OHRM/test_data/add_employee_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\orangeHrm_project\OHRM_Project\PROJECT_OHRM\test_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABB36792-39AE-42F4-A9F4-7A3EC1E6950D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67C93F8D-8A1D-4535-8C05-ED9E2F17F128}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
   <si>
     <t>fname</t>
   </si>
@@ -54,10 +54,7 @@
     <t>k</t>
   </si>
   <si>
-    <t>rabajiman</t>
-  </si>
-  <si>
-    <t>rabajiman@123</t>
+    <t>ramanan@123</t>
   </si>
 </sst>
 </file>
@@ -414,13 +411,13 @@
         <v>8</v>
       </c>
       <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="F2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/PROJECT_OHRM/test_data/add_employee_data.xlsx
+++ b/PROJECT_OHRM/test_data/add_employee_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\orangeHrm_project\OHRM_Project\PROJECT_OHRM\test_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67C93F8D-8A1D-4535-8C05-ED9E2F17F128}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E90C5C2B-2AFE-48E2-8898-AEDBDB675C9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
   <si>
     <t>fname</t>
   </si>
@@ -55,6 +55,9 @@
   </si>
   <si>
     <t>ramanan@123</t>
+  </si>
+  <si>
+    <t>ramanans</t>
   </si>
 </sst>
 </file>
@@ -90,9 +93,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -411,12 +413,12 @@
         <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" t="s">
         <v>9</v>
       </c>
     </row>

--- a/PROJECT_OHRM/test_data/add_employee_data.xlsx
+++ b/PROJECT_OHRM/test_data/add_employee_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\orangeHrm_project\OHRM_Project\PROJECT_OHRM\test_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E90C5C2B-2AFE-48E2-8898-AEDBDB675C9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE6021BC-7899-4CB3-B3EB-CBF24F3B460B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -57,7 +57,7 @@
     <t>ramanan@123</t>
   </si>
   <si>
-    <t>ramanans</t>
+    <t>ramanpk</t>
   </si>
 </sst>
 </file>

--- a/PROJECT_OHRM/test_data/add_employee_data.xlsx
+++ b/PROJECT_OHRM/test_data/add_employee_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\orangeHrm_project\OHRM_Project\PROJECT_OHRM\test_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE6021BC-7899-4CB3-B3EB-CBF24F3B460B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF1C4358-933A-429C-B3B4-85B07EB2AB49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,9 +45,6 @@
     <t>cpword</t>
   </si>
   <si>
-    <t>ramanan</t>
-  </si>
-  <si>
     <t>balaji</t>
   </si>
   <si>
@@ -57,7 +54,10 @@
     <t>ramanan@123</t>
   </si>
   <si>
-    <t>ramanpk</t>
+    <t>krishna</t>
+  </si>
+  <si>
+    <t>ramanpaji1</t>
   </si>
 </sst>
 </file>
@@ -378,6 +378,7 @@
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="4" max="4" width="11.21875" customWidth="1"/>
     <col min="5" max="5" width="14.5546875" customWidth="1"/>
     <col min="6" max="6" width="14.77734375" customWidth="1"/>
   </cols>
@@ -404,22 +405,22 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/PROJECT_OHRM/test_data/add_employee_data.xlsx
+++ b/PROJECT_OHRM/test_data/add_employee_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\orangeHrm_project\OHRM_Project\PROJECT_OHRM\test_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF1C4358-933A-429C-B3B4-85B07EB2AB49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3179A2D7-DC3C-411D-A71B-791E234E4921}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1116" yWindow="1116" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -45,19 +45,19 @@
     <t>cpword</t>
   </si>
   <si>
-    <t>balaji</t>
-  </si>
-  <si>
     <t>k</t>
   </si>
   <si>
-    <t>ramanan@123</t>
-  </si>
-  <si>
-    <t>krishna</t>
-  </si>
-  <si>
-    <t>ramanpaji1</t>
+    <t>ram</t>
+  </si>
+  <si>
+    <t>charan</t>
+  </si>
+  <si>
+    <t>charanram</t>
+  </si>
+  <si>
+    <t>charan@123</t>
   </si>
 </sst>
 </file>
@@ -93,8 +93,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -405,22 +406,22 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="E2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>8</v>
+      <c r="F2" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
